--- a/basedatos_partidas/salida/descompuestos/CT-06-05-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-05-030.xlsx
@@ -539,10 +539,10 @@
         <v>5.2</v>
       </c>
       <c r="G10" t="n">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.18</v>
+        <v>0.105</v>
       </c>
       <c r="H11" t="n">
-        <v>1.62</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +591,10 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="H12" t="n">
-        <v>1.28</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.8</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="14">
@@ -750,10 +750,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>10.23</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="23">
@@ -769,7 +769,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>10.33</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-06-05-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-05-030.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H23"/>
+  <dimension ref="A3:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MT-MOR-PEGA</t>
+          <t>MT-CEMENTO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -558,218 +558,244 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Mortero de pega para mampostería, elaborado con cemento y arena lavada.</t>
+          <t>Cemento Portland gris tipo I, en saco. Para mortero de pega y mortero de friso.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>5.46</v>
       </c>
       <c r="G11" t="n">
-        <v>0.105</v>
+        <v>0.225</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MT-MOR-FRISO</t>
+          <t>MT-ARENA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Mortero de friso para revestimiento de paramentos, elaborado con cemento y arena cernida.</t>
+          <t>Arena lavada de río, puesta en obra, para camas de asiento y rellenos de zanja. Para mortero de pega y mortero de friso.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>0.01785</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>22</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="13">
-      <c r="F13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MT-AGUA-OBRA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Agua para amasado, humectación de rellenos y compactación. Para mortero de pega y mortero de friso.</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.00356</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>Subtotal materiales:</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>4.96</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="H14" t="n">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Equipo y maquinaria</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>MQ-MEZCL</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Mezcladora de concreto y mortero de 1 saco, incluida amortización y combustible.</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>0.06</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G16" t="n">
         <v>3.6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal equipo y maquinaria:</t>
-        </is>
       </c>
       <c r="H16" t="n">
         <v>0.22</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal equipo y maquinaria:</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>Mano de obra</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MO-OF1-ALB</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Oficial de 1ª albañil.</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.09</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>MO-OF1-ALB</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Oficial de 1ª albañil.</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>MO-AYU</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Ayudante.</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F20" t="n">
         <v>0.32</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G20" t="n">
         <v>3.5</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H20" t="n">
         <v>1.12</v>
       </c>
     </row>
-    <row r="20">
-      <c r="F20" s="1" t="inlineStr">
+    <row r="21">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Subtotal mano de obra:</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>3.21</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="22">
+      <c r="A22" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="D22" t="inlineStr">
+    <row r="23">
+      <c r="D23" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="G23" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="H23" t="n">
         <v>0.08</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Costes directos (1+2+3+4):</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="5" t="n">
-        <v>8.470000000000001</v>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="5" t="n">
+        <v>8.359999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-06-05-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-05-030.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 06 Paredes y tabiquería</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Dinteles, brocales y remates de vano</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
